--- a/GBDS JULY FILES 2026/PRICE LIST January.xlsx
+++ b/GBDS JULY FILES 2026/PRICE LIST January.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6204722E-D796-4226-9F5D-6D6C1AC4A1E6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1F063E-BDA9-4F00-AFF5-C9432E99C56C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="420" windowWidth="29040" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/GBDS JULY FILES 2026/PRICE LIST January.xlsx
+++ b/GBDS JULY FILES 2026/PRICE LIST January.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1F063E-BDA9-4F00-AFF5-C9432E99C56C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE057502-7665-4309-9F9B-0CE9CD22AC08}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
